--- a/starter/src/main/resources/static/downloads/file/微语产品报价单.xlsx
+++ b/starter/src/main/resources/static/downloads/file/微语产品报价单.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15680"/>
+    <workbookView windowWidth="26380" windowHeight="14840"/>
   </bookViews>
   <sheets>
     <sheet name="微语 产品报价单" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>报价日期：</t>
   </si>
   <si>
-    <t>25 年 7 月 14 日</t>
+    <t>26 年 4 月 22 日</t>
   </si>
   <si>
     <t>有效期限：</t>
@@ -194,6 +194,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF1F2329"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.5"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
@@ -211,14 +219,6 @@
       <b/>
       <sz val="9.75"/>
       <color rgb="FF8EB2A8"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -624,6 +624,19 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -676,10 +689,38 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFBDD7EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDD7EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDD7EE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF8EB2A8"/>
       </left>
       <right style="thin">
         <color rgb="FF8EAAD8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EB2A8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EAAD8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EB2A8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF8EB2A8"/>
       </right>
       <top style="thin">
         <color rgb="FF8EB2A8"/>
@@ -706,45 +747,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF8EB2A8"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF8EB2A8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF8EB2A8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF8EAAD8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF8EB2A8"/>
       </left>
       <right style="thin">
@@ -760,14 +762,12 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBDD7EE"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFBDD7EE"/>
+        <color rgb="FFFFFFFF"/>
       </right>
-      <top style="thin">
-        <color rgb="FFBDD7EE"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1036,80 +1036,80 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1531,18 +1531,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="27"/>
+      <c r="J3" s="9"/>
       <c r="K3" s="3"/>
       <c r="L3" s="1"/>
     </row>
@@ -1551,12 +1551,12 @@
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="3"/>
       <c r="L4" s="1"/>
     </row>
@@ -1565,23 +1565,23 @@
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="27"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="3"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" ht="68" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="6"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -1594,115 +1594,115 @@
     </row>
     <row r="7" ht="26" spans="1:12">
       <c r="A7" s="1"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="9" t="s">
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="3"/>
       <c r="L7" s="1"/>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:12">
       <c r="A8" s="1"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="15"/>
       <c r="K8" s="2"/>
       <c r="L8" s="1"/>
     </row>
     <row r="9" ht="17.6" spans="1:12">
       <c r="A9" s="1"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
     </row>
     <row r="10" ht="17.6" spans="1:12">
       <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
     </row>
     <row r="11" ht="17.6" spans="1:12">
       <c r="A11" s="1"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
       <c r="K11" s="3"/>
       <c r="L11" s="1"/>
     </row>
     <row r="12" ht="16" spans="1:12">
       <c r="A12" s="1"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="21" t="s">
         <v>21</v>
       </c>
       <c r="K12" s="3"/>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="1"/>
-      <c r="B13" s="15"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="2">
         <v>1</v>
       </c>
@@ -1720,30 +1720,30 @@
       <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="23">
-        <v>50000</v>
-      </c>
-      <c r="G13" s="23">
+      <c r="F13" s="22">
+        <v>59800</v>
+      </c>
+      <c r="G13" s="22">
         <f t="shared" ref="G13:G20" si="0">E13*F13</f>
-        <v>50000</v>
-      </c>
-      <c r="H13" s="24">
+        <v>59800</v>
+      </c>
+      <c r="H13" s="23">
         <v>0.03</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f t="shared" ref="I13:I20" si="1">G13*H13</f>
-        <v>1500</v>
-      </c>
-      <c r="J13" s="23">
+        <v>1794</v>
+      </c>
+      <c r="J13" s="22">
         <f t="shared" ref="J13:J20" si="2">G13+I13</f>
-        <v>51500</v>
+        <v>61594</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
-      <c r="B14" s="15"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="2">
         <v>2</v>
       </c>
@@ -1753,30 +1753,30 @@
       <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="23">
-        <v>50000</v>
-      </c>
-      <c r="G14" s="23">
+      <c r="F14" s="22">
+        <v>59800</v>
+      </c>
+      <c r="G14" s="22">
         <f t="shared" si="0"/>
-        <v>50000</v>
-      </c>
-      <c r="H14" s="24">
+        <v>59800</v>
+      </c>
+      <c r="H14" s="23">
         <v>0.03</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f t="shared" si="1"/>
-        <v>1500</v>
-      </c>
-      <c r="J14" s="23">
+        <v>1794</v>
+      </c>
+      <c r="J14" s="22">
         <f t="shared" si="2"/>
-        <v>51500</v>
+        <v>61594</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1"/>
-      <c r="B15" s="15"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="2">
         <v>3</v>
       </c>
@@ -1786,30 +1786,30 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="23">
-        <v>50000</v>
-      </c>
-      <c r="G15" s="23">
+      <c r="F15" s="22">
+        <v>59800</v>
+      </c>
+      <c r="G15" s="22">
         <f t="shared" si="0"/>
-        <v>50000</v>
-      </c>
-      <c r="H15" s="24">
+        <v>59800</v>
+      </c>
+      <c r="H15" s="23">
         <v>0.03</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <f t="shared" si="1"/>
-        <v>1500</v>
-      </c>
-      <c r="J15" s="23">
+        <v>1794</v>
+      </c>
+      <c r="J15" s="22">
         <f t="shared" si="2"/>
-        <v>51500</v>
+        <v>61594</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="1"/>
-      <c r="B16" s="15"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="2">
         <v>4</v>
       </c>
@@ -1819,30 +1819,30 @@
       <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="23">
-        <v>50000</v>
-      </c>
-      <c r="G16" s="23">
+      <c r="F16" s="22">
+        <v>59800</v>
+      </c>
+      <c r="G16" s="22">
         <f t="shared" si="0"/>
-        <v>50000</v>
-      </c>
-      <c r="H16" s="24">
+        <v>59800</v>
+      </c>
+      <c r="H16" s="23">
         <v>0.03</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <f t="shared" si="1"/>
-        <v>1500</v>
-      </c>
-      <c r="J16" s="23">
+        <v>1794</v>
+      </c>
+      <c r="J16" s="22">
         <f t="shared" si="2"/>
-        <v>51500</v>
+        <v>61594</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="1"/>
-      <c r="B17" s="15"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="2">
         <v>5</v>
       </c>
@@ -1852,30 +1852,30 @@
       <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="F17" s="23">
-        <v>20000</v>
-      </c>
-      <c r="G17" s="23">
+      <c r="F17" s="22">
+        <v>39800</v>
+      </c>
+      <c r="G17" s="22">
         <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="H17" s="24">
+        <v>39800</v>
+      </c>
+      <c r="H17" s="23">
         <v>0.03</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="J17" s="23">
+        <v>1194</v>
+      </c>
+      <c r="J17" s="22">
         <f t="shared" si="2"/>
-        <v>20600</v>
+        <v>40994</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
-      <c r="B18" s="15"/>
+      <c r="B18" s="19"/>
       <c r="C18" s="2">
         <v>6</v>
       </c>
@@ -1883,17 +1883,17 @@
         <v>27</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23">
+      <c r="F18" s="22"/>
+      <c r="G18" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="23">
+      <c r="H18" s="23"/>
+      <c r="I18" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="1"/>
-      <c r="B19" s="15"/>
+      <c r="B19" s="19"/>
       <c r="C19" s="2">
         <v>7</v>
       </c>
@@ -1910,17 +1910,17 @@
         <v>28</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23">
+      <c r="F19" s="22"/>
+      <c r="G19" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="23">
+      <c r="H19" s="23"/>
+      <c r="I19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1929,23 +1929,23 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="1"/>
-      <c r="B20" s="15"/>
+      <c r="B20" s="19"/>
       <c r="C20" s="2">
         <v>8</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23">
+      <c r="F20" s="22"/>
+      <c r="G20" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="23">
+      <c r="H20" s="23"/>
+      <c r="I20" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1954,70 +1954,70 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="19"/>
+      <c r="C21" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="25"/>
       <c r="I21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="22">
         <f>SUM(G13:G20)</f>
-        <v>220000</v>
+        <v>279000</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="25"/>
       <c r="I22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="22">
         <f>SUM(I13:I20)</f>
-        <v>6600</v>
+        <v>8370</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" ht="18" spans="1:12">
       <c r="A23" s="1"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="29" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="29">
         <f>J21+J22</f>
-        <v>226600</v>
+        <v>287370</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
       <c r="G24" s="2"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
-      <c r="B25" s="15"/>
+      <c r="B25" s="19"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
